--- a/portfolio/posts/_data/IceDates.xlsx
+++ b/portfolio/posts/_data/IceDates.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Nebagamon" sheetId="1" r:id="rId1"/>
@@ -265,7 +265,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2030" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2031" uniqueCount="288">
   <si>
     <t>iceOut</t>
   </si>
@@ -1126,6 +1126,9 @@
   </si>
   <si>
     <t>2024-25</t>
+  </si>
+  <si>
+    <t>2025-2026</t>
   </si>
 </sst>
 </file>
@@ -13678,7 +13681,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="3" width="10.33203125" customWidth="1"/>
@@ -13906,6 +13909,14 @@
       </c>
       <c r="C30" s="1">
         <v>45762</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>287</v>
+      </c>
+      <c r="C31" s="1">
+        <v>46130</v>
       </c>
     </row>
   </sheetData>
